--- a/deposits_example.xlsx
+++ b/deposits_example.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="16">
   <si>
     <t xml:space="preserve">deposit_date</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t xml:space="preserve">usd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">usd_eft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">efectivo</t>
   </si>
   <si>
     <t xml:space="preserve">Portfolio_1</t>
@@ -174,14 +180,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="13.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="27.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="27.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -208,8 +214,8 @@
       <c r="A2" s="2" t="n">
         <v>43994</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1011.03</v>
+      <c r="B2" s="1" t="n">
+        <v>5000</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>6</v>
@@ -220,56 +226,59 @@
       <c r="E2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F2" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
-        <v>44177</v>
+        <v>43994</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>1</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
-        <v>44178</v>
+        <v>44177</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>-453</v>
+        <v>1019.72</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
-        <v>44359</v>
+        <v>44178</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>1011.03</v>
+        <v>-453</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>1</v>
@@ -277,16 +286,16 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
-        <v>44542</v>
+        <v>44359</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>1</v>
@@ -294,16 +303,16 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
-        <v>44724</v>
+        <v>44542</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>1011.03</v>
+        <v>1019.72</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>1</v>
@@ -311,16 +320,16 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
-        <v>44907</v>
+        <v>44724</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>1</v>
@@ -328,16 +337,16 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
-        <v>45089</v>
+        <v>44907</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>1011.03</v>
+        <v>1019.72</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>1</v>
@@ -345,16 +354,16 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
-        <v>45272</v>
+        <v>45089</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>1</v>
@@ -362,16 +371,16 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
-        <v>45455</v>
+        <v>45272</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>1011.03</v>
+        <v>1019.72</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>1</v>
@@ -379,16 +388,16 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
-        <v>45638</v>
+        <v>45455</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>1</v>
@@ -396,16 +405,16 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
-        <v>45850</v>
+        <v>45638</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>1037.78</v>
+        <v>1019.72</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>1</v>
@@ -413,16 +422,16 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
-        <v>46003</v>
+        <v>45850</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>1856.3</v>
+        <v>1037.78</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>1</v>
@@ -430,16 +439,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
-        <v>45881</v>
+        <v>46003</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>1961.75</v>
+        <v>1856.3</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>1</v>
@@ -447,53 +456,53 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
-        <v>45882</v>
+        <v>45881</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>1031.51</v>
+        <v>1961.75</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>1</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
-        <v>46023</v>
+        <v>45882</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>1954.45</v>
+        <v>1031.51</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>1013.95</v>
+        <v>1954.45</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>1</v>
@@ -501,53 +510,53 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
-        <v>46055</v>
+        <v>46024</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>-500</v>
+        <v>1013.95</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="0" t="n">
         <v>1</v>
-      </c>
-      <c r="F19" s="0" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
-        <v>46025</v>
+        <v>46055</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>1067.29</v>
+        <v>-500</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>1080.83</v>
+        <v>1067.29</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>1</v>
@@ -555,16 +564,16 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>1127.79</v>
+        <v>1080.83</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>1</v>
@@ -572,16 +581,16 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="n">
-        <v>43994</v>
+        <v>46027</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>1011.03</v>
+        <v>1127.79</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>1</v>
@@ -589,53 +598,53 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="n">
-        <v>44177</v>
+        <v>43994</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E24" s="0" t="n">
         <v>1</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="n">
-        <v>44178</v>
+        <v>44177</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>-453</v>
+        <v>1019.72</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="n">
-        <v>44359</v>
+        <v>44178</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>1011.03</v>
+        <v>-453</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="0" t="n">
         <v>1</v>
@@ -643,16 +652,16 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="n">
-        <v>44542</v>
+        <v>44359</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E27" s="0" t="n">
         <v>1</v>
@@ -660,53 +669,53 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="n">
-        <v>44724</v>
+        <v>44542</v>
       </c>
       <c r="B28" s="0" t="n">
-        <v>1011.03</v>
+        <v>1019.72</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>235</v>
-      </c>
-      <c r="F28" s="0" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="n">
-        <v>44907</v>
+        <v>44724</v>
       </c>
       <c r="B29" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>1</v>
+        <v>235</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="n">
-        <v>45089</v>
+        <v>44907</v>
       </c>
       <c r="B30" s="0" t="n">
-        <v>1011.03</v>
+        <v>1019.72</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E30" s="0" t="n">
         <v>1</v>
@@ -714,16 +723,16 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="n">
-        <v>45272</v>
+        <v>45089</v>
       </c>
       <c r="B31" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>1</v>
@@ -731,16 +740,16 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="n">
-        <v>45455</v>
+        <v>45272</v>
       </c>
       <c r="B32" s="0" t="n">
-        <v>1011.03</v>
+        <v>1019.72</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E32" s="0" t="n">
         <v>1</v>
@@ -748,16 +757,16 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="n">
-        <v>45638</v>
+        <v>45455</v>
       </c>
       <c r="B33" s="0" t="n">
-        <v>1019.72</v>
+        <v>1011.03</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E33" s="0" t="n">
         <v>1</v>
@@ -765,16 +774,16 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="n">
-        <v>45850</v>
+        <v>45638</v>
       </c>
       <c r="B34" s="0" t="n">
-        <v>1037.78</v>
+        <v>1019.72</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E34" s="0" t="n">
         <v>1</v>
@@ -782,16 +791,16 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="n">
-        <v>46003</v>
+        <v>45850</v>
       </c>
       <c r="B35" s="0" t="n">
-        <v>1856.3</v>
+        <v>1037.78</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E35" s="0" t="n">
         <v>1</v>
@@ -799,16 +808,16 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="n">
-        <v>45881</v>
+        <v>46003</v>
       </c>
       <c r="B36" s="0" t="n">
-        <v>1961.75</v>
+        <v>1856.3</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E36" s="0" t="n">
         <v>1</v>
@@ -816,53 +825,53 @@
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="n">
-        <v>45882</v>
+        <v>45881</v>
       </c>
       <c r="B37" s="0" t="n">
-        <v>1031.51</v>
+        <v>1961.75</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E37" s="0" t="n">
         <v>1</v>
-      </c>
-      <c r="F37" s="0" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="n">
-        <v>46023</v>
+        <v>45882</v>
       </c>
       <c r="B38" s="0" t="n">
-        <v>1954.45</v>
+        <v>1031.51</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D38" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="0" t="s">
         <v>11</v>
-      </c>
-      <c r="E38" s="0" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="B39" s="0" t="n">
-        <v>1013.95</v>
+        <v>1954.45</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E39" s="0" t="n">
         <v>1</v>
@@ -870,53 +879,53 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="n">
-        <v>46055</v>
+        <v>46024</v>
       </c>
       <c r="B40" s="0" t="n">
-        <v>-500</v>
+        <v>1013.95</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E40" s="0" t="n">
         <v>1</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="n">
-        <v>46025</v>
+        <v>46055</v>
       </c>
       <c r="B41" s="0" t="n">
-        <v>1067.29</v>
+        <v>-500</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="n">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="B42" s="0" t="n">
-        <v>1080.83</v>
+        <v>1067.29</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E42" s="0" t="n">
         <v>1</v>
@@ -924,18 +933,35 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="n">
+        <v>46026</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>1080.83</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="n">
         <v>46027</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B44" s="0" t="n">
         <v>1127.79</v>
       </c>
-      <c r="C43" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="0" t="n">
+      <c r="C44" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/deposits_example.xlsx
+++ b/deposits_example.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="20">
   <si>
     <t xml:space="preserve">deposit_date</t>
   </si>
@@ -43,10 +43,7 @@
     <t xml:space="preserve">usd</t>
   </si>
   <si>
-    <t xml:space="preserve">usd_eft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">efectivo</t>
+    <t xml:space="preserve">cash</t>
   </si>
   <si>
     <t xml:space="preserve">Portfolio_1</t>
@@ -68,6 +65,21 @@
   </si>
   <si>
     <t xml:space="preserve">one deposit in ARS. CCL rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fixed_Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">first capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interest_pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">second capita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">return capital</t>
   </si>
 </sst>
 </file>
@@ -180,7 +192,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.1"/>
@@ -227,7 +239,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -241,7 +253,7 @@
         <v>6</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>1</v>
@@ -258,13 +270,13 @@
         <v>6</v>
       </c>
       <c r="D4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="0" t="s">
         <v>9</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -278,7 +290,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>1</v>
@@ -295,7 +307,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>1</v>
@@ -312,7 +324,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>1</v>
@@ -329,7 +341,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>1</v>
@@ -346,7 +358,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>1</v>
@@ -363,7 +375,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>1</v>
@@ -380,7 +392,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>1</v>
@@ -397,7 +409,7 @@
         <v>6</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>1</v>
@@ -414,7 +426,7 @@
         <v>6</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>1</v>
@@ -431,7 +443,7 @@
         <v>6</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="0" t="n">
         <v>1</v>
@@ -448,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="0" t="n">
         <v>1</v>
@@ -465,7 +477,7 @@
         <v>6</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="0" t="n">
         <v>1</v>
@@ -482,13 +494,13 @@
         <v>6</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -502,7 +514,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>1</v>
@@ -519,7 +531,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="0" t="n">
         <v>1</v>
@@ -536,13 +548,13 @@
         <v>6</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -556,7 +568,7 @@
         <v>6</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="0" t="n">
         <v>1</v>
@@ -573,7 +585,7 @@
         <v>6</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" s="0" t="n">
         <v>1</v>
@@ -590,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="0" t="n">
         <v>1</v>
@@ -607,7 +619,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="0" t="n">
         <v>1</v>
@@ -624,13 +636,13 @@
         <v>6</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -644,7 +656,7 @@
         <v>6</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" s="0" t="n">
         <v>1</v>
@@ -661,7 +673,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" s="0" t="n">
         <v>1</v>
@@ -678,7 +690,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" s="0" t="n">
         <v>1</v>
@@ -692,16 +704,16 @@
         <v>1011.03</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" s="0" t="n">
         <v>235</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -715,7 +727,7 @@
         <v>6</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E30" s="0" t="n">
         <v>1</v>
@@ -732,7 +744,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>1</v>
@@ -749,7 +761,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E32" s="0" t="n">
         <v>1</v>
@@ -766,7 +778,7 @@
         <v>6</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33" s="0" t="n">
         <v>1</v>
@@ -783,7 +795,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" s="0" t="n">
         <v>1</v>
@@ -800,7 +812,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35" s="0" t="n">
         <v>1</v>
@@ -817,7 +829,7 @@
         <v>6</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36" s="0" t="n">
         <v>1</v>
@@ -834,7 +846,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37" s="0" t="n">
         <v>1</v>
@@ -851,13 +863,13 @@
         <v>6</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -871,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39" s="0" t="n">
         <v>1</v>
@@ -888,7 +900,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" s="0" t="n">
         <v>1</v>
@@ -905,13 +917,13 @@
         <v>6</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -925,7 +937,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E42" s="0" t="n">
         <v>1</v>
@@ -942,7 +954,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E43" s="0" t="n">
         <v>1</v>
@@ -959,10 +971,250 @@
         <v>6</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44" s="0" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="n">
+        <v>43831</v>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="n">
+        <v>43922</v>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>-400</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="n">
+        <v>44013</v>
+      </c>
+      <c r="B47" s="0" t="n">
+        <v>-400</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B48" s="0" t="n">
+        <v>-400</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B49" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B50" s="0" t="n">
+        <v>-600</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B51" s="0" t="n">
+        <v>-600</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B52" s="0" t="n">
+        <v>-600</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B53" s="0" t="n">
+        <v>-600</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B54" s="0" t="n">
+        <v>-600</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>-600</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/deposits_example.xlsx
+++ b/deposits_example.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="21">
   <si>
     <t xml:space="preserve">deposit_date</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t xml:space="preserve">some comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tag:gotta withdraw something</t>
   </si>
   <si>
     <t xml:space="preserve">more comments for this deposit</t>
@@ -193,7 +196,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.52"/>
@@ -295,6 +298,9 @@
       <c r="E5" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="F5" s="0" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
@@ -500,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -554,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -619,7 +625,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24" s="0" t="n">
         <v>1</v>
@@ -636,7 +642,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" s="0" t="n">
         <v>1</v>
@@ -656,7 +662,7 @@
         <v>6</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="0" t="n">
         <v>1</v>
@@ -673,7 +679,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27" s="0" t="n">
         <v>1</v>
@@ -690,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E28" s="0" t="n">
         <v>1</v>
@@ -704,16 +710,16 @@
         <v>1011.03</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" s="0" t="n">
         <v>235</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -727,7 +733,7 @@
         <v>6</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E30" s="0" t="n">
         <v>1</v>
@@ -744,7 +750,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>1</v>
@@ -761,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32" s="0" t="n">
         <v>1</v>
@@ -778,7 +784,7 @@
         <v>6</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33" s="0" t="n">
         <v>1</v>
@@ -795,7 +801,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34" s="0" t="n">
         <v>1</v>
@@ -812,7 +818,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35" s="0" t="n">
         <v>1</v>
@@ -829,7 +835,7 @@
         <v>6</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E36" s="0" t="n">
         <v>1</v>
@@ -846,7 +852,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E37" s="0" t="n">
         <v>1</v>
@@ -863,13 +869,13 @@
         <v>6</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -883,7 +889,7 @@
         <v>6</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E39" s="0" t="n">
         <v>1</v>
@@ -900,7 +906,7 @@
         <v>6</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E40" s="0" t="n">
         <v>1</v>
@@ -917,13 +923,13 @@
         <v>6</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E41" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -937,7 +943,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E42" s="0" t="n">
         <v>1</v>
@@ -954,7 +960,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E43" s="0" t="n">
         <v>1</v>
@@ -971,7 +977,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E44" s="0" t="n">
         <v>1</v>
@@ -988,13 +994,13 @@
         <v>6</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E45" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1008,13 +1014,13 @@
         <v>6</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E46" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1028,13 +1034,13 @@
         <v>6</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E47" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1048,13 +1054,13 @@
         <v>6</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E48" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1068,13 +1074,13 @@
         <v>6</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1088,13 +1094,13 @@
         <v>6</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E50" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1108,13 +1114,13 @@
         <v>6</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E51" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1128,13 +1134,13 @@
         <v>6</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E52" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1148,13 +1154,13 @@
         <v>6</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1168,13 +1174,13 @@
         <v>6</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1188,13 +1194,13 @@
         <v>6</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E55" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1208,13 +1214,13 @@
         <v>6</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E56" s="0" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
